--- a/Aug_2026/daily Reports/STT Report Elite Marketing AUG_26.xlsx
+++ b/Aug_2026/daily Reports/STT Report Elite Marketing AUG_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C3A877-58AE-44C1-921D-4A3C61F0DD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435D9C18-65B7-4DC7-8436-A7B411378AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="489">
   <si>
     <t>Date</t>
   </si>
@@ -1476,6 +1476,27 @@
   <si>
     <t>Periode : 01 to 18 AUG,2026</t>
   </si>
+  <si>
+    <t>Kamal Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sm Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machiz Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanza Bakers </t>
+  </si>
+  <si>
+    <t>Umair Bakery</t>
+  </si>
+  <si>
+    <t>Ali Store</t>
+  </si>
+  <si>
+    <t>Usaman Store</t>
+  </si>
 </sst>
 </file>
 
@@ -2422,10 +2443,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2434,16 +2458,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2829,47 +2850,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="123" t="s">
+      <c r="A1" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="C1" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="E1" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="F1" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="G1" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="123" t="s">
+      <c r="H1" s="119" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J1" s="42"/>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="125" t="s">
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="121" t="s">
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="122" t="s">
         <v>10</v>
       </c>
       <c r="T1" s="124" t="s">
@@ -2884,61 +2905,61 @@
       <c r="Y1" s="124"/>
       <c r="Z1" s="124"/>
       <c r="AA1" s="124"/>
-      <c r="AB1" s="121" t="s">
+      <c r="AB1" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="121" t="s">
+      <c r="AC1" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="121" t="s">
+      <c r="AD1" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="121" t="s">
+      <c r="AE1" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="121" t="s">
+      <c r="AF1" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="121" t="s">
+      <c r="AG1" s="122" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="84">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="121" t="s">
+      <c r="AI1" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="121" t="s">
+      <c r="AJ1" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="121" t="s">
+      <c r="AK1" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="121" t="s">
+      <c r="AL1" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="121" t="s">
+      <c r="AM1" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="119" t="s">
+      <c r="AN1" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="119" t="s">
+      <c r="AO1" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="121" t="s">
+      <c r="AP1" s="122" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="123"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
+      <c r="A2" s="119"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -2969,7 +2990,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="122"/>
+      <c r="S2" s="123"/>
       <c r="T2" s="83" t="s">
         <v>73</v>
       </c>
@@ -2994,23 +3015,23 @@
       <c r="AA2" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="123"/>
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
       <c r="AH2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="120"/>
-      <c r="AO2" s="120"/>
-      <c r="AP2" s="122"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="123"/>
+      <c r="AL2" s="123"/>
+      <c r="AM2" s="123"/>
+      <c r="AN2" s="126"/>
+      <c r="AO2" s="126"/>
+      <c r="AP2" s="123"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="85">
@@ -42801,33 +42822,63 @@
       <c r="AP393" s="92"/>
     </row>
     <row r="394" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A394" s="85"/>
-      <c r="B394" s="51"/>
-      <c r="C394" s="97"/>
-      <c r="D394" s="97"/>
-      <c r="E394" s="48"/>
-      <c r="F394" s="116"/>
-      <c r="G394" s="116"/>
-      <c r="H394" s="116"/>
-      <c r="I394" s="117"/>
+      <c r="A394" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B394" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C394" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D394" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E394" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F394" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G394" s="116" t="s">
+        <v>482</v>
+      </c>
+      <c r="H394" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I394" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J394" s="48"/>
-      <c r="K394" s="105"/>
-      <c r="L394" s="105"/>
-      <c r="M394" s="105"/>
+      <c r="K394" s="105">
+        <v>6</v>
+      </c>
+      <c r="L394" s="105">
+        <v>6</v>
+      </c>
+      <c r="M394" s="105">
+        <v>6</v>
+      </c>
       <c r="N394" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="O394" s="86"/>
-      <c r="P394" s="86"/>
-      <c r="Q394" s="86"/>
+        <v>18</v>
+      </c>
+      <c r="O394" s="86">
+        <v>6</v>
+      </c>
+      <c r="P394" s="86">
+        <v>6</v>
+      </c>
+      <c r="Q394" s="86">
+        <v>6</v>
+      </c>
       <c r="R394" s="104">
         <f t="shared" si="116"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S394" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="T394" s="87"/>
       <c r="U394" s="87"/>
@@ -42848,14 +42899,14 @@
       </c>
       <c r="AE394" s="89">
         <f t="shared" si="110"/>
-        <v>0</v>
+        <v>3559.3649999999998</v>
       </c>
       <c r="AF394" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG394" s="4">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>231.35872499999999</v>
       </c>
       <c r="AH394" s="49">
         <f t="shared" si="111"/>
@@ -42863,32 +42914,52 @@
       </c>
       <c r="AI394" s="89">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>3328.0062749999997</v>
       </c>
       <c r="AJ394" s="91">
         <v>0.18</v>
       </c>
       <c r="AK394" s="5">
         <f t="shared" si="113"/>
-        <v>0</v>
+        <v>599.0411294999999</v>
       </c>
       <c r="AL394" s="89">
         <f t="shared" si="114"/>
-        <v>0</v>
+        <v>3927.0474044999996</v>
       </c>
       <c r="AP394" s="92"/>
     </row>
     <row r="395" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A395" s="85"/>
-      <c r="B395" s="51"/>
-      <c r="C395" s="97"/>
-      <c r="D395" s="97"/>
-      <c r="E395" s="48"/>
-      <c r="F395" s="116"/>
-      <c r="G395" s="116"/>
-      <c r="H395" s="116"/>
-      <c r="I395" s="117"/>
-      <c r="J395" s="48"/>
+      <c r="A395" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B395" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C395" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D395" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E395" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F395" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G395" s="116" t="s">
+        <v>281</v>
+      </c>
+      <c r="H395" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I395" s="117" t="s">
+        <v>284</v>
+      </c>
+      <c r="J395" s="48">
+        <v>6</v>
+      </c>
       <c r="K395" s="105"/>
       <c r="L395" s="105"/>
       <c r="M395" s="105"/>
@@ -42905,7 +42976,7 @@
       </c>
       <c r="S395" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T395" s="87"/>
       <c r="U395" s="87"/>
@@ -42926,53 +42997,77 @@
       </c>
       <c r="AE395" s="89">
         <f t="shared" si="110"/>
-        <v>0</v>
+        <v>671.46</v>
       </c>
       <c r="AF395" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG395" s="4">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>43.644900000000007</v>
       </c>
       <c r="AH395" s="49">
         <f t="shared" si="111"/>
-        <v>0</v>
+        <v>8.2467000000000006</v>
       </c>
       <c r="AI395" s="89">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>627.81510000000003</v>
       </c>
       <c r="AJ395" s="91">
         <v>0.18</v>
       </c>
       <c r="AK395" s="5">
         <f t="shared" si="113"/>
-        <v>0</v>
+        <v>113.00671800000001</v>
       </c>
       <c r="AL395" s="89">
         <f t="shared" si="114"/>
-        <v>0</v>
+        <v>740.82181800000001</v>
       </c>
       <c r="AP395" s="92"/>
     </row>
     <row r="396" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A396" s="85"/>
-      <c r="B396" s="51"/>
-      <c r="C396" s="97"/>
-      <c r="D396" s="97"/>
-      <c r="E396" s="48"/>
-      <c r="F396" s="116"/>
-      <c r="G396" s="116"/>
-      <c r="H396" s="116"/>
-      <c r="I396" s="117"/>
+      <c r="A396" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B396" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C396" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D396" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E396" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F396" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G396" s="116" t="s">
+        <v>483</v>
+      </c>
+      <c r="H396" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I396" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J396" s="48"/>
-      <c r="K396" s="86"/>
-      <c r="L396" s="86"/>
-      <c r="M396" s="86"/>
+      <c r="K396" s="86">
+        <v>20</v>
+      </c>
+      <c r="L396" s="86">
+        <v>20</v>
+      </c>
+      <c r="M396" s="86">
+        <v>20</v>
+      </c>
       <c r="N396" s="104">
         <f t="shared" si="117"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O396" s="86"/>
       <c r="P396" s="86"/>
@@ -42983,7 +43078,7 @@
       </c>
       <c r="S396" s="86">
         <f t="shared" si="118"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T396" s="87"/>
       <c r="U396" s="87"/>
@@ -43004,14 +43099,14 @@
       </c>
       <c r="AE396" s="89">
         <f t="shared" si="110"/>
-        <v>0</v>
+        <v>7506.15</v>
       </c>
       <c r="AF396" s="90">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG396" s="4">
         <f t="shared" si="115"/>
-        <v>0</v>
+        <v>487.89974999999998</v>
       </c>
       <c r="AH396" s="49">
         <f t="shared" si="111"/>
@@ -43019,31 +43114,49 @@
       </c>
       <c r="AI396" s="89">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>7018.2502500000001</v>
       </c>
       <c r="AJ396" s="91">
         <v>0.18</v>
       </c>
       <c r="AK396" s="5">
         <f t="shared" si="113"/>
-        <v>0</v>
+        <v>1263.2850449999999</v>
       </c>
       <c r="AL396" s="89">
         <f t="shared" si="114"/>
-        <v>0</v>
+        <v>8281.5352949999997</v>
       </c>
       <c r="AP396" s="92"/>
     </row>
     <row r="397" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A397" s="85"/>
-      <c r="B397" s="51"/>
-      <c r="C397" s="97"/>
-      <c r="D397" s="97"/>
-      <c r="E397" s="48"/>
-      <c r="F397" s="96"/>
-      <c r="G397" s="116"/>
-      <c r="H397" s="116"/>
-      <c r="I397" s="117"/>
+      <c r="A397" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B397" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C397" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D397" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E397" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F397" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G397" s="116" t="s">
+        <v>484</v>
+      </c>
+      <c r="H397" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I397" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J397" s="48"/>
       <c r="K397" s="105"/>
       <c r="L397" s="105"/>
@@ -43113,15 +43226,33 @@
       <c r="AP397" s="92"/>
     </row>
     <row r="398" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A398" s="85"/>
-      <c r="B398" s="51"/>
-      <c r="C398" s="97"/>
-      <c r="D398" s="97"/>
-      <c r="E398" s="48"/>
-      <c r="F398" s="96"/>
-      <c r="G398" s="116"/>
-      <c r="H398" s="116"/>
-      <c r="I398" s="117"/>
+      <c r="A398" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B398" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C398" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D398" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E398" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F398" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G398" s="116" t="s">
+        <v>403</v>
+      </c>
+      <c r="H398" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I398" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J398" s="48"/>
       <c r="K398" s="105"/>
       <c r="L398" s="105"/>
@@ -43191,15 +43322,33 @@
       <c r="AP398" s="92"/>
     </row>
     <row r="399" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A399" s="85"/>
-      <c r="B399" s="51"/>
-      <c r="C399" s="97"/>
-      <c r="D399" s="97"/>
-      <c r="E399" s="48"/>
-      <c r="F399" s="96"/>
-      <c r="G399" s="116"/>
-      <c r="H399" s="116"/>
-      <c r="I399" s="117"/>
+      <c r="A399" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B399" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C399" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D399" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E399" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F399" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G399" s="116" t="s">
+        <v>485</v>
+      </c>
+      <c r="H399" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I399" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J399" s="48"/>
       <c r="K399" s="105"/>
       <c r="L399" s="105"/>
@@ -43269,15 +43418,33 @@
       <c r="AP399" s="92"/>
     </row>
     <row r="400" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A400" s="85"/>
-      <c r="B400" s="51"/>
-      <c r="C400" s="97"/>
-      <c r="D400" s="97"/>
-      <c r="E400" s="48"/>
-      <c r="F400" s="96"/>
-      <c r="G400" s="116"/>
-      <c r="H400" s="116"/>
-      <c r="I400" s="117"/>
+      <c r="A400" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B400" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C400" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D400" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E400" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F400" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G400" s="116" t="s">
+        <v>486</v>
+      </c>
+      <c r="H400" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I400" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J400" s="48"/>
       <c r="K400" s="86"/>
       <c r="L400" s="86"/>
@@ -43347,15 +43514,33 @@
       <c r="AP400" s="92"/>
     </row>
     <row r="401" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A401" s="85"/>
-      <c r="B401" s="51"/>
-      <c r="C401" s="97"/>
-      <c r="D401" s="97"/>
-      <c r="E401" s="48"/>
-      <c r="F401" s="96"/>
-      <c r="G401" s="116"/>
-      <c r="H401" s="116"/>
-      <c r="I401" s="117"/>
+      <c r="A401" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B401" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C401" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D401" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E401" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F401" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G401" s="116" t="s">
+        <v>487</v>
+      </c>
+      <c r="H401" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I401" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J401" s="48"/>
       <c r="K401" s="86"/>
       <c r="L401" s="86"/>
@@ -43425,15 +43610,33 @@
       <c r="AP401" s="92"/>
     </row>
     <row r="402" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A402" s="85"/>
-      <c r="B402" s="51"/>
-      <c r="C402" s="97"/>
-      <c r="D402" s="97"/>
-      <c r="E402" s="48"/>
-      <c r="F402" s="96"/>
-      <c r="G402" s="96"/>
-      <c r="H402" s="96"/>
-      <c r="I402" s="3"/>
+      <c r="A402" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B402" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C402" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D402" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E402" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F402" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="G402" s="116" t="s">
+        <v>488</v>
+      </c>
+      <c r="H402" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="I402" s="117" t="s">
+        <v>284</v>
+      </c>
       <c r="J402" s="48"/>
       <c r="K402" s="105"/>
       <c r="L402" s="105"/>
@@ -43503,12 +43706,24 @@
       <c r="AP402" s="92"/>
     </row>
     <row r="403" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A403" s="85"/>
-      <c r="B403" s="51"/>
-      <c r="C403" s="97"/>
-      <c r="D403" s="97"/>
-      <c r="E403" s="48"/>
-      <c r="F403" s="96"/>
+      <c r="A403" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B403" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C403" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D403" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E403" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F403" s="116" t="s">
+        <v>87</v>
+      </c>
       <c r="G403" s="75"/>
       <c r="H403" s="96"/>
       <c r="I403" s="3"/>
@@ -43581,12 +43796,24 @@
       <c r="AP403" s="92"/>
     </row>
     <row r="404" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A404" s="85"/>
-      <c r="B404" s="51"/>
-      <c r="C404" s="97"/>
-      <c r="D404" s="97"/>
-      <c r="E404" s="48"/>
-      <c r="F404" s="96"/>
+      <c r="A404" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B404" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C404" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D404" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E404" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F404" s="116" t="s">
+        <v>87</v>
+      </c>
       <c r="G404" s="75"/>
       <c r="H404" s="96"/>
       <c r="I404" s="3"/>
@@ -43659,12 +43886,24 @@
       <c r="AP404" s="92"/>
     </row>
     <row r="405" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A405" s="85"/>
-      <c r="B405" s="51"/>
-      <c r="C405" s="97"/>
-      <c r="D405" s="97"/>
-      <c r="E405" s="48"/>
-      <c r="F405" s="96"/>
+      <c r="A405" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B405" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C405" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D405" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E405" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F405" s="116" t="s">
+        <v>87</v>
+      </c>
       <c r="G405" s="75"/>
       <c r="H405" s="96"/>
       <c r="I405" s="3"/>
@@ -43737,12 +43976,24 @@
       <c r="AP405" s="92"/>
     </row>
     <row r="406" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A406" s="85"/>
-      <c r="B406" s="51"/>
-      <c r="C406" s="97"/>
-      <c r="D406" s="97"/>
-      <c r="E406" s="48"/>
-      <c r="F406" s="96"/>
+      <c r="A406" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B406" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C406" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D406" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E406" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F406" s="116" t="s">
+        <v>87</v>
+      </c>
       <c r="G406" s="75"/>
       <c r="H406" s="96"/>
       <c r="I406" s="3"/>
@@ -43815,11 +44066,21 @@
       <c r="AP406" s="92"/>
     </row>
     <row r="407" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A407" s="85"/>
-      <c r="B407" s="51"/>
-      <c r="C407" s="97"/>
-      <c r="D407" s="97"/>
-      <c r="E407" s="48"/>
+      <c r="A407" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B407" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C407" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D407" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E407" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F407" s="96"/>
       <c r="G407" s="75"/>
       <c r="H407" s="96"/>
@@ -43893,11 +44154,21 @@
       <c r="AP407" s="92"/>
     </row>
     <row r="408" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A408" s="85"/>
-      <c r="B408" s="51"/>
-      <c r="C408" s="97"/>
-      <c r="D408" s="97"/>
-      <c r="E408" s="48"/>
+      <c r="A408" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B408" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C408" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D408" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E408" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F408" s="96"/>
       <c r="G408" s="75"/>
       <c r="H408" s="96"/>
@@ -43971,11 +44242,21 @@
       <c r="AP408" s="92"/>
     </row>
     <row r="409" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A409" s="85"/>
-      <c r="B409" s="51"/>
-      <c r="C409" s="97"/>
-      <c r="D409" s="97"/>
-      <c r="E409" s="48"/>
+      <c r="A409" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B409" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C409" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D409" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E409" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F409" s="96"/>
       <c r="G409" s="75"/>
       <c r="H409" s="96"/>
@@ -44049,11 +44330,21 @@
       <c r="AP409" s="92"/>
     </row>
     <row r="410" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A410" s="85"/>
-      <c r="B410" s="51"/>
-      <c r="C410" s="97"/>
-      <c r="D410" s="97"/>
-      <c r="E410" s="48"/>
+      <c r="A410" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B410" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C410" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D410" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E410" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F410" s="96"/>
       <c r="G410" s="75"/>
       <c r="H410" s="96"/>
@@ -44127,11 +44418,21 @@
       <c r="AP410" s="92"/>
     </row>
     <row r="411" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A411" s="85"/>
-      <c r="B411" s="51"/>
-      <c r="C411" s="97"/>
-      <c r="D411" s="97"/>
-      <c r="E411" s="48"/>
+      <c r="A411" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B411" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C411" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D411" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E411" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F411" s="96"/>
       <c r="G411" s="75"/>
       <c r="H411" s="96"/>
@@ -44205,11 +44506,21 @@
       <c r="AP411" s="92"/>
     </row>
     <row r="412" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A412" s="85"/>
-      <c r="B412" s="51"/>
-      <c r="C412" s="97"/>
-      <c r="D412" s="97"/>
-      <c r="E412" s="48"/>
+      <c r="A412" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B412" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C412" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D412" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E412" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F412" s="96"/>
       <c r="G412" s="75"/>
       <c r="H412" s="96"/>
@@ -44283,11 +44594,21 @@
       <c r="AP412" s="92"/>
     </row>
     <row r="413" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A413" s="85"/>
-      <c r="B413" s="51"/>
-      <c r="C413" s="97"/>
-      <c r="D413" s="97"/>
-      <c r="E413" s="48"/>
+      <c r="A413" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B413" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C413" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D413" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E413" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F413" s="96"/>
       <c r="G413" s="75"/>
       <c r="H413" s="96"/>
@@ -44361,10 +44682,21 @@
       <c r="AP413" s="92"/>
     </row>
     <row r="414" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A414" s="98"/>
-      <c r="C414" s="87"/>
-      <c r="D414" s="99"/>
-      <c r="E414" s="3"/>
+      <c r="A414" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B414" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C414" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D414" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E414" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F414" s="96"/>
       <c r="G414" s="96"/>
       <c r="H414" s="96"/>
@@ -44438,10 +44770,21 @@
       <c r="AP414" s="92"/>
     </row>
     <row r="415" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A415" s="98"/>
-      <c r="C415" s="87"/>
-      <c r="D415" s="99"/>
-      <c r="E415" s="3"/>
+      <c r="A415" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B415" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C415" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D415" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E415" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F415" s="96"/>
       <c r="G415" s="96"/>
       <c r="H415" s="96"/>
@@ -44515,10 +44858,21 @@
       <c r="AP415" s="92"/>
     </row>
     <row r="416" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A416" s="98"/>
-      <c r="C416" s="87"/>
-      <c r="D416" s="99"/>
-      <c r="E416" s="3"/>
+      <c r="A416" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B416" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C416" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D416" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E416" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F416" s="96"/>
       <c r="G416" s="96"/>
       <c r="H416" s="96"/>
@@ -44592,10 +44946,21 @@
       <c r="AP416" s="92"/>
     </row>
     <row r="417" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A417" s="98"/>
-      <c r="C417" s="87"/>
-      <c r="D417" s="99"/>
-      <c r="E417" s="3"/>
+      <c r="A417" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B417" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C417" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D417" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E417" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F417" s="96"/>
       <c r="G417" s="96"/>
       <c r="H417" s="96"/>
@@ -44669,10 +45034,21 @@
       <c r="AP417" s="92"/>
     </row>
     <row r="418" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A418" s="98"/>
-      <c r="C418" s="87"/>
-      <c r="D418" s="99"/>
-      <c r="E418" s="3"/>
+      <c r="A418" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B418" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C418" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D418" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E418" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F418" s="96"/>
       <c r="G418" s="96"/>
       <c r="H418" s="96"/>
@@ -44746,10 +45122,21 @@
       <c r="AP418" s="92"/>
     </row>
     <row r="419" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A419" s="98"/>
-      <c r="C419" s="87"/>
-      <c r="D419" s="99"/>
-      <c r="E419" s="3"/>
+      <c r="A419" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B419" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C419" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D419" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E419" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F419" s="96"/>
       <c r="G419" s="96"/>
       <c r="H419" s="96"/>
@@ -44823,10 +45210,21 @@
       <c r="AP419" s="92"/>
     </row>
     <row r="420" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A420" s="98"/>
-      <c r="C420" s="87"/>
-      <c r="D420" s="99"/>
-      <c r="E420" s="3"/>
+      <c r="A420" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B420" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C420" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D420" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E420" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F420" s="96"/>
       <c r="G420" s="96"/>
       <c r="H420" s="96"/>
@@ -44900,10 +45298,21 @@
       <c r="AP420" s="92"/>
     </row>
     <row r="421" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A421" s="98"/>
-      <c r="C421" s="87"/>
-      <c r="D421" s="99"/>
-      <c r="E421" s="3"/>
+      <c r="A421" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B421" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C421" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D421" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E421" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F421" s="96"/>
       <c r="G421" s="96"/>
       <c r="H421" s="96"/>
@@ -44977,10 +45386,21 @@
       <c r="AP421" s="92"/>
     </row>
     <row r="422" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A422" s="98"/>
-      <c r="C422" s="87"/>
-      <c r="D422" s="99"/>
-      <c r="E422" s="3"/>
+      <c r="A422" s="85">
+        <v>46253</v>
+      </c>
+      <c r="B422" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C422" s="97">
+        <v>546456</v>
+      </c>
+      <c r="D422" s="97">
+        <v>156165</v>
+      </c>
+      <c r="E422" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="F422" s="96"/>
       <c r="G422" s="96"/>
       <c r="H422" s="96"/>
@@ -45865,28 +46285,28 @@
       <c r="AD433" s="100"/>
       <c r="AE433" s="100">
         <f>SUM(AE3:AE432)</f>
-        <v>7120401.3475000001</v>
+        <v>7132138.3225000007</v>
       </c>
       <c r="AF433" s="78"/>
       <c r="AG433" s="100">
         <f>SUM(AG3:AG432)</f>
-        <v>622308.64246250049</v>
+        <v>623071.54583750048</v>
       </c>
       <c r="AH433" s="100">
         <f>SUM(AH3:AH432)</f>
-        <v>15113.452199999987</v>
+        <v>15121.698899999987</v>
       </c>
       <c r="AI433" s="100">
         <f>SUM(AI3:AI432)</f>
-        <v>6498037.7270375015</v>
+        <v>6509011.7986625014</v>
       </c>
       <c r="AK433" s="100">
         <f>SUM(AK3:AK432)</f>
-        <v>1169646.7908667517</v>
+        <v>1171622.1237592516</v>
       </c>
       <c r="AL433" s="100">
         <f>SUM(AL3:AL432)</f>
-        <v>7667684.5179042481</v>
+        <v>7680633.9224217478</v>
       </c>
       <c r="AP433" s="92"/>
     </row>
@@ -68213,43 +68633,43 @@
       <c r="A861" s="3"/>
       <c r="J861" s="107">
         <f>SUM(J3:J860)</f>
-        <v>11002</v>
+        <v>11008</v>
       </c>
       <c r="K861" s="107">
         <f t="shared" ref="K861:S861" si="176">SUM(K3:K860)</f>
-        <v>6877</v>
+        <v>6903</v>
       </c>
       <c r="L861" s="107">
         <f t="shared" si="176"/>
-        <v>6998</v>
+        <v>7024</v>
       </c>
       <c r="M861" s="107">
         <f t="shared" si="176"/>
-        <v>8412</v>
+        <v>8438</v>
       </c>
       <c r="N861" s="107">
         <f t="shared" si="176"/>
-        <v>22287</v>
+        <v>22365</v>
       </c>
       <c r="O861" s="107">
         <f t="shared" si="176"/>
-        <v>13726</v>
+        <v>13732</v>
       </c>
       <c r="P861" s="107">
         <f t="shared" si="176"/>
-        <v>12727</v>
+        <v>12733</v>
       </c>
       <c r="Q861" s="107">
         <f t="shared" si="176"/>
-        <v>16285</v>
+        <v>16291</v>
       </c>
       <c r="R861" s="107">
         <f t="shared" si="176"/>
-        <v>42738</v>
+        <v>42756</v>
       </c>
       <c r="S861" s="107">
         <f t="shared" si="176"/>
-        <v>76027</v>
+        <v>76129</v>
       </c>
       <c r="AP861" s="7"/>
     </row>
@@ -68316,43 +68736,43 @@
       </c>
       <c r="J864" s="47">
         <f>J861/40</f>
-        <v>275.05</v>
+        <v>275.2</v>
       </c>
       <c r="K864" s="109">
         <f t="shared" ref="K864:S864" si="177">K861/40</f>
-        <v>171.92500000000001</v>
+        <v>172.57499999999999</v>
       </c>
       <c r="L864" s="109">
         <f t="shared" si="177"/>
-        <v>174.95</v>
+        <v>175.6</v>
       </c>
       <c r="M864" s="109">
         <f t="shared" si="177"/>
-        <v>210.3</v>
+        <v>210.95</v>
       </c>
       <c r="N864" s="47">
         <f t="shared" si="177"/>
-        <v>557.17499999999995</v>
+        <v>559.125</v>
       </c>
       <c r="O864" s="109">
         <f t="shared" si="177"/>
-        <v>343.15</v>
+        <v>343.3</v>
       </c>
       <c r="P864" s="109">
         <f t="shared" si="177"/>
-        <v>318.17500000000001</v>
+        <v>318.32499999999999</v>
       </c>
       <c r="Q864" s="109">
         <f t="shared" si="177"/>
-        <v>407.125</v>
+        <v>407.27499999999998</v>
       </c>
       <c r="R864" s="47">
         <f t="shared" si="177"/>
-        <v>1068.45</v>
+        <v>1068.9000000000001</v>
       </c>
       <c r="S864" s="109">
         <f t="shared" si="177"/>
-        <v>1900.675</v>
+        <v>1903.2249999999999</v>
       </c>
       <c r="T864" s="54">
         <f t="shared" ref="T864:AF864" si="178">+T433/40</f>
@@ -68397,7 +68817,7 @@
       </c>
       <c r="AE864" s="43">
         <f t="shared" si="178"/>
-        <v>178010.03368749999</v>
+        <v>178303.45806250002</v>
       </c>
       <c r="AF864" s="43">
         <f t="shared" si="178"/>
@@ -68417,7 +68837,7 @@
     <row r="866" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S866" s="53">
         <f>S864+W864+AA864</f>
-        <v>1900.675</v>
+        <v>1903.2249999999999</v>
       </c>
       <c r="X866" t="s">
         <v>50</v>
@@ -68428,13 +68848,14 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -68447,14 +68868,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -68526,11 +68946,11 @@
       </c>
       <c r="G7" s="16">
         <f>'STT Report'!Q864+'STT Report'!Z864</f>
-        <v>407.125</v>
+        <v>407.27499999999998</v>
       </c>
       <c r="H7" s="17">
         <f>E7+F7-G7</f>
-        <v>286.72500000000002</v>
+        <v>286.57500000000005</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -68545,11 +68965,11 @@
       </c>
       <c r="G8" s="16">
         <f>'STT Report'!P864+'STT Report'!Y864</f>
-        <v>318.17500000000001</v>
+        <v>318.32499999999999</v>
       </c>
       <c r="H8" s="17">
         <f>E8+F8-G8</f>
-        <v>191.495</v>
+        <v>191.34500000000003</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -68564,11 +68984,11 @@
       </c>
       <c r="G9" s="16">
         <f>'STT Report'!O864+'STT Report'!X864</f>
-        <v>343.15</v>
+        <v>343.3</v>
       </c>
       <c r="H9" s="17">
         <f>E9+F9-G9</f>
-        <v>285.30000000000007</v>
+        <v>285.15000000000003</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -68585,11 +69005,11 @@
       </c>
       <c r="G10" s="22">
         <f>SUM(G7:G9)</f>
-        <v>1068.4499999999998</v>
+        <v>1068.8999999999999</v>
       </c>
       <c r="H10" s="23">
         <f>SUM(H7:H9)</f>
-        <v>763.5200000000001</v>
+        <v>763.07000000000016</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -68604,11 +69024,11 @@
       </c>
       <c r="G11" s="44">
         <f>'STT Report'!J864</f>
-        <v>275.05</v>
+        <v>275.2</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>575.31999999999994</v>
+        <v>575.17000000000007</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -68645,11 +69065,11 @@
       </c>
       <c r="G14" s="20">
         <f>SUM(G11:G13)</f>
-        <v>275.05</v>
+        <v>275.2</v>
       </c>
       <c r="H14" s="23">
         <f>SUM(H11:H13)</f>
-        <v>575.31999999999994</v>
+        <v>575.17000000000007</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -68664,11 +69084,11 @@
       </c>
       <c r="G15" s="16">
         <f>'STT Report'!M864+'STT Report'!V864</f>
-        <v>210.3</v>
+        <v>210.95</v>
       </c>
       <c r="H15" s="17">
         <f>E15+F15-G15</f>
-        <v>273.71999999999997</v>
+        <v>273.07</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -68683,11 +69103,11 @@
       </c>
       <c r="G16" s="16">
         <f>'STT Report'!L864+'STT Report'!U864</f>
-        <v>174.95</v>
+        <v>175.6</v>
       </c>
       <c r="H16" s="17">
         <f>E16+F16-G16</f>
-        <v>203.47000000000003</v>
+        <v>202.82000000000002</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -68702,11 +69122,11 @@
       </c>
       <c r="G17" s="16">
         <f>'STT Report'!K864+'STT Report'!T864</f>
-        <v>171.92500000000001</v>
+        <v>172.57499999999999</v>
       </c>
       <c r="H17" s="17">
         <f>E17+F17-G17</f>
-        <v>297.29500000000002</v>
+        <v>296.64500000000004</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -68723,11 +69143,11 @@
       </c>
       <c r="G18" s="22">
         <f>SUM(G15:G17)</f>
-        <v>557.17499999999995</v>
+        <v>559.125</v>
       </c>
       <c r="H18" s="23">
         <f>SUM(H15:H17)</f>
-        <v>774.48500000000001</v>
+        <v>772.53500000000008</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -68744,11 +69164,11 @@
       </c>
       <c r="G19" s="25">
         <f>G10+G14+G18</f>
-        <v>1900.6749999999997</v>
+        <v>1903.2249999999999</v>
       </c>
       <c r="H19" s="27">
         <f>H10+H14+H18</f>
-        <v>2113.3250000000003</v>
+        <v>2110.7750000000005</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
